--- a/ТЗ/Уведомления — дополнение (наша система).xlsx
+++ b/ТЗ/Уведомления — дополнение (наша система).xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="Дополнение — уведомления" sheetId="1" r:id="rId1"/>
-    <sheet name="Каналы и роли (поправки)" sheetId="2" r:id="rId2"/>
+    <sheet name="Каналы связи (справочник)" sheetId="2" r:id="rId2"/>
+    <sheet name="Каналы и роли (поправки)" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -1437,6 +1438,283 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="54" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Канал</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Тип</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Для кого</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Назначение / когда используется</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В системе (центр уведомлений)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Внутренний</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оператор, Бухгалтер, Менеджер, Админ</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Колокольчик в CRM — базовый канал, всегда включён</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-mail</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Внешний</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оператор и Клиент</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Документы, КП, счета; юридически значимые уведомления</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telegram</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мессенджер</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оператор и Клиент</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оперативные пуши по заявкам, дедлайнам, чату</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAX</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мессенджер</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оператор и Клиент</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Основной мессенджер в чатах CRM (наравне с Telegram)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WhatsApp</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мессенджер</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Клиент (и оператор)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Связь с клиентом там, где он привык; резерв для важных</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Внешний</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Клиент (и оператор)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Резервный канал для критичных: оплата, тайм-лимит, дедлайн</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Звонок / Телефон</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Внешний</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оператор и Клиент</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Входящие звонки по заявке; эскалация критичных событий</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Push (моб. приложение)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Внешний</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оператор и Клиент</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мгновенные уведомления в мобильном приложении</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Desktop (браузер)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Внутренний</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оператор, Бухгалтер</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Всплывающие уведомления на рабочем месте</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WebApp (личный кабинет)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Внешний</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Клиент</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">События кабинета: статусы заказа, документы, напоминания</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API / Система</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Служебный</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оператор, Админ, Техадмин(=Админ)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Служебные события интеграций, синхронизация, коды ошибок</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
@@ -1468,7 +1746,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мессенджер</t>
+          <t xml:space="preserve">Мессенджеры</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1478,120 +1756,142 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAX (канал чатов в CRM)</t>
+          <t xml:space="preserve">Telegram + MAX (MAX — основной мессенджер в чатах CRM)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Заменить «Telegram» → «MAX» по всему списку (или «MAX/Telegram», если планируются оба)</t>
+          <t xml:space="preserve">Оставить Telegram, добавить MAX; в критичных дублировать в оба</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каналы (полный набор)</t>
+          <t xml:space="preserve">Каналы доставки оператору (из профиля)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRM, Telegram, Email, WebApp</t>
+          <t xml:space="preserve">Email, Telegram</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRM (внутри системы), MAX, Email, Телефон, WebApp (личный кабинет), API/Система (служебные)</t>
+          <t xml:space="preserve">В системе (центр уведомлений), E-mail, Telegram, MAX, WhatsApp, SMS, Push (моб. прил.), Desktop (браузер)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Добавить «Телефон» для входящих звонков и «WebApp» для событий кабинета</t>
+          <t xml:space="preserve">Полный набор задаётся в Профиль → Уведомления → Каналы доставки</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Роль «Супервайзер»</t>
+          <t xml:space="preserve">Каналы клиента</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Супервайзер</t>
+          <t xml:space="preserve">Telegram, Email, WebApp</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Менеджер (линейный руководитель)</t>
+          <t xml:space="preserve">MAX, Telegram, WhatsApp, Email, SMS, WebApp (личный кабинет), Телефон</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Читать «Супервайзер» как «Менеджер»</t>
+          <t xml:space="preserve">Клиенту слать по подключённому каналу; SMS/Звонок — резерв для критичных</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Роль «Техадмин»</t>
+          <t xml:space="preserve">Роль «Супервайзер»</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Техадмин</t>
+          <t xml:space="preserve">Супервайзер</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Админ</t>
+          <t xml:space="preserve">Менеджер (линейный руководитель)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Функции техадмина закрыты ролью «Админ»</t>
+          <t xml:space="preserve">Читать «Супервайзер» как «Менеджер»</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Роли (наш набор)</t>
+          <t xml:space="preserve">Роль «Техадмин»</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Клиент, Оператор, Бухгалтер, Супервайзер, Админ, Техадмин</t>
+          <t xml:space="preserve">Техадмин</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Клиент, Оператор, Бухгалтер, Менеджер, Админ</t>
+          <t xml:space="preserve">Админ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Согласовать названия ролей с матрицей прав в «Настройки → Роли и права»</t>
+          <t xml:space="preserve">Функции техадмина закрыты ролью «Админ»</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Роли (наш набор)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Клиент, Оператор, Бухгалтер, Супервайзер, Админ, Техадмин</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Клиент, Оператор, Бухгалтер, Менеджер, Админ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Согласовать названия ролей с матрицей прав в «Настройки → Роли и права»</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Категория «Интеграции»</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t xml:space="preserve">Разрозненные ошибки API</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">Отдельная категория уведомлений + справочник кодов (GDS-503, TKT-500, PAY-402…)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ошибки интеграций слать в категорию «Интеграции» с кодом и ссылкой на справочник</t>
         </is>
